--- a/samples/meridian-growth-partners-iii-call-4.xlsx
+++ b/samples/meridian-growth-partners-iii-call-4.xlsx
@@ -1649,7 +1649,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Expected Output — regression fixture</v>
+        <v>Expected Output — golden test case</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -1705,7 +1705,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>The engine compares its own result against these rows on every compute.</v>
+        <v>Figures produced by the delivered spec engine. The app checks its own result against them.</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>126857.5</v>
       </c>
       <c r="M12">
-        <v>80499.99999999999</v>
+        <v>80500</v>
       </c>
       <c r="N12">
         <v>46357.5</v>
@@ -2313,10 +2313,10 @@
         <v>11181357.5</v>
       </c>
       <c r="Q12">
-        <v>51218642.50000001</v>
+        <v>51218642.5</v>
       </c>
       <c r="R12">
-        <v>44901357.49999999</v>
+        <v>44901357.5</v>
       </c>
     </row>
   </sheetData>

--- a/samples/meridian-growth-partners-iii-call-4.xlsx
+++ b/samples/meridian-growth-partners-iii-call-4.xlsx
@@ -9,7 +9,6 @@
     <sheet name="Call_Components" sheetId="4" r:id="rId4"/>
     <sheet name="Management_Fee" sheetId="5" r:id="rId5"/>
     <sheet name="Transfers" sheetId="6" r:id="rId6"/>
-    <sheet name="Expected_Output" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -403,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -457,22 +456,32 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v xml:space="preserve">  Expected_Output   Regression fixture. The engine checks its result against it.</v>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v/>
+        <v>This tab, and any tab not listed above, is ignored.</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>This tab, and any tab not listed above, is ignored.</v>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>There is no expected-output tab: the allocation sheet is what the app</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>produces from these inputs, not something you fill in.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A15"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1641,687 +1650,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:K3"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R12"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Expected Output — golden test case</v>
-      </c>
-      <c r="B1" t="str">
-        <v/>
-      </c>
-      <c r="C1" t="str">
-        <v/>
-      </c>
-      <c r="D1" t="str">
-        <v/>
-      </c>
-      <c r="E1" t="str">
-        <v/>
-      </c>
-      <c r="F1" t="str">
-        <v/>
-      </c>
-      <c r="G1" t="str">
-        <v/>
-      </c>
-      <c r="H1" t="str">
-        <v/>
-      </c>
-      <c r="I1" t="str">
-        <v/>
-      </c>
-      <c r="J1" t="str">
-        <v/>
-      </c>
-      <c r="K1" t="str">
-        <v/>
-      </c>
-      <c r="L1" t="str">
-        <v/>
-      </c>
-      <c r="M1" t="str">
-        <v/>
-      </c>
-      <c r="N1" t="str">
-        <v/>
-      </c>
-      <c r="O1" t="str">
-        <v/>
-      </c>
-      <c r="P1" t="str">
-        <v/>
-      </c>
-      <c r="Q1" t="str">
-        <v/>
-      </c>
-      <c r="R1" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Figures produced by the delivered spec engine. The app checks its own result against them.</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v/>
-      </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
-        <v/>
-      </c>
-      <c r="R2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>LP_ID</v>
-      </c>
-      <c r="B3" t="str">
-        <v>LP_Name</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Commitment</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Opening_UCC</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Opening_Paid_In</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Project_Helios</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Project_Orion</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Bridge_Facility_Repayment</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Fund_Operating_Expenses</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Formation_Cost_True_Up</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Fee_Rate</v>
-      </c>
-      <c r="L3" t="str">
-        <v>Fee_Gross</v>
-      </c>
-      <c r="M3" t="str">
-        <v>Fee_Offset</v>
-      </c>
-      <c r="N3" t="str">
-        <v>Fee_Net</v>
-      </c>
-      <c r="O3" t="str">
-        <v>Total_Call</v>
-      </c>
-      <c r="P3" t="str">
-        <v>Reduces_Unfunded_Amt</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>Closing_UCC</v>
-      </c>
-      <c r="R3" t="str">
-        <v>Closing_Paid_In</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>LP01</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Northbridge Retirement System</v>
-      </c>
-      <c r="C4">
-        <v>25000000</v>
-      </c>
-      <c r="D4">
-        <v>16250000</v>
-      </c>
-      <c r="E4">
-        <v>8750000</v>
-      </c>
-      <c r="F4">
-        <v>1614583.33</v>
-      </c>
-      <c r="G4">
-        <v>885416.67</v>
-      </c>
-      <c r="H4">
-        <v>325520.83</v>
-      </c>
-      <c r="I4">
-        <v>74218.75</v>
-      </c>
-      <c r="J4">
-        <v>31250</v>
-      </c>
-      <c r="K4">
-        <v>0.0175</v>
-      </c>
-      <c r="L4">
-        <v>33687.5</v>
-      </c>
-      <c r="M4">
-        <v>21377.09</v>
-      </c>
-      <c r="N4">
-        <v>12310.41</v>
-      </c>
-      <c r="O4">
-        <v>2943299.99</v>
-      </c>
-      <c r="P4">
-        <v>2912049.99</v>
-      </c>
-      <c r="Q4">
-        <v>13337950.01</v>
-      </c>
-      <c r="R4">
-        <v>11693299.99</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>LP02</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Kestrel University Endowment</v>
-      </c>
-      <c r="C5">
-        <v>12000000</v>
-      </c>
-      <c r="D5">
-        <v>7800000</v>
-      </c>
-      <c r="E5">
-        <v>4200000</v>
-      </c>
-      <c r="F5">
-        <v>775000</v>
-      </c>
-      <c r="G5">
-        <v>425000</v>
-      </c>
-      <c r="H5">
-        <v>156250</v>
-      </c>
-      <c r="I5">
-        <v>35625</v>
-      </c>
-      <c r="J5">
-        <v>15000</v>
-      </c>
-      <c r="K5">
-        <v>0.0175</v>
-      </c>
-      <c r="L5">
-        <v>16170</v>
-      </c>
-      <c r="M5">
-        <v>10261.01</v>
-      </c>
-      <c r="N5">
-        <v>5908.99</v>
-      </c>
-      <c r="O5">
-        <v>1412783.99</v>
-      </c>
-      <c r="P5">
-        <v>1397783.99</v>
-      </c>
-      <c r="Q5">
-        <v>6402216.01</v>
-      </c>
-      <c r="R5">
-        <v>5612783.99</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>LP03</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Tanaka Family Holdings KK</v>
-      </c>
-      <c r="C6">
-        <v>6000000</v>
-      </c>
-      <c r="D6">
-        <v>3900000</v>
-      </c>
-      <c r="E6">
-        <v>2100000</v>
-      </c>
-      <c r="F6">
-        <v>387500</v>
-      </c>
-      <c r="G6">
-        <v>212500</v>
-      </c>
-      <c r="H6">
-        <v>78125</v>
-      </c>
-      <c r="I6">
-        <v>17812.5</v>
-      </c>
-      <c r="J6">
-        <v>7500</v>
-      </c>
-      <c r="K6">
-        <v>0.015</v>
-      </c>
-      <c r="L6">
-        <v>6930</v>
-      </c>
-      <c r="M6">
-        <v>4397.57</v>
-      </c>
-      <c r="N6">
-        <v>2532.43</v>
-      </c>
-      <c r="O6">
-        <v>705969.93</v>
-      </c>
-      <c r="P6">
-        <v>698469.93</v>
-      </c>
-      <c r="Q6">
-        <v>3201530.07</v>
-      </c>
-      <c r="R6">
-        <v>2805969.93</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>LP04</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Arbor Mutual Assurance</v>
-      </c>
-      <c r="C7">
-        <v>30000000</v>
-      </c>
-      <c r="D7">
-        <v>19500000</v>
-      </c>
-      <c r="E7">
-        <v>10500000</v>
-      </c>
-      <c r="F7">
-        <v>1937500</v>
-      </c>
-      <c r="G7">
-        <v>1062500</v>
-      </c>
-      <c r="H7">
-        <v>390625</v>
-      </c>
-      <c r="I7">
-        <v>89062.49</v>
-      </c>
-      <c r="J7">
-        <v>37500</v>
-      </c>
-      <c r="K7">
-        <v>0.0175</v>
-      </c>
-      <c r="L7">
-        <v>40425</v>
-      </c>
-      <c r="M7">
-        <v>25652.5</v>
-      </c>
-      <c r="N7">
-        <v>14772.5</v>
-      </c>
-      <c r="O7">
-        <v>3531959.99</v>
-      </c>
-      <c r="P7">
-        <v>3494459.99</v>
-      </c>
-      <c r="Q7">
-        <v>16005540.01</v>
-      </c>
-      <c r="R7">
-        <v>14031959.99</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>LP05</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Halvorsen Nominees Limited</v>
-      </c>
-      <c r="C8">
-        <v>9500000</v>
-      </c>
-      <c r="D8">
-        <v>6175000</v>
-      </c>
-      <c r="E8">
-        <v>3325000</v>
-      </c>
-      <c r="F8">
-        <v>613541.67</v>
-      </c>
-      <c r="G8">
-        <v>336458.33</v>
-      </c>
-      <c r="H8">
-        <v>123697.92</v>
-      </c>
-      <c r="I8">
-        <v>28203.13</v>
-      </c>
-      <c r="J8">
-        <v>11875</v>
-      </c>
-      <c r="K8">
-        <v>0.0175</v>
-      </c>
-      <c r="L8">
-        <v>12801.25</v>
-      </c>
-      <c r="M8">
-        <v>8123.29</v>
-      </c>
-      <c r="N8">
-        <v>4677.96</v>
-      </c>
-      <c r="O8">
-        <v>1118454.01</v>
-      </c>
-      <c r="P8">
-        <v>1106579.01</v>
-      </c>
-      <c r="Q8">
-        <v>5068420.99</v>
-      </c>
-      <c r="R8">
-        <v>4443454.01</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>LP06</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Sycamore Foundation</v>
-      </c>
-      <c r="C9">
-        <v>4500000</v>
-      </c>
-      <c r="D9">
-        <v>2925000</v>
-      </c>
-      <c r="E9">
-        <v>1575000</v>
-      </c>
-      <c r="F9">
-        <v>290625</v>
-      </c>
-      <c r="G9">
-        <v>159375</v>
-      </c>
-      <c r="H9">
-        <v>58593.75</v>
-      </c>
-      <c r="I9">
-        <v>13359.38</v>
-      </c>
-      <c r="J9">
-        <v>5625</v>
-      </c>
-      <c r="K9">
-        <v>0.0175</v>
-      </c>
-      <c r="L9">
-        <v>6063.75</v>
-      </c>
-      <c r="M9">
-        <v>3847.87</v>
-      </c>
-      <c r="N9">
-        <v>2215.88</v>
-      </c>
-      <c r="O9">
-        <v>529794.01</v>
-      </c>
-      <c r="P9">
-        <v>524169.01</v>
-      </c>
-      <c r="Q9">
-        <v>2400830.99</v>
-      </c>
-      <c r="R9">
-        <v>2104794.01</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>LP07</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Bridgeline Capital SCSp</v>
-      </c>
-      <c r="C10">
-        <v>8000000</v>
-      </c>
-      <c r="D10">
-        <v>5200000</v>
-      </c>
-      <c r="E10">
-        <v>2800000</v>
-      </c>
-      <c r="F10">
-        <v>516666.67</v>
-      </c>
-      <c r="G10">
-        <v>283333.33</v>
-      </c>
-      <c r="H10">
-        <v>104166.67</v>
-      </c>
-      <c r="I10">
-        <v>23750</v>
-      </c>
-      <c r="J10">
-        <v>10000</v>
-      </c>
-      <c r="K10">
-        <v>0.0175</v>
-      </c>
-      <c r="L10">
-        <v>10780</v>
-      </c>
-      <c r="M10">
-        <v>6840.67</v>
-      </c>
-      <c r="N10">
-        <v>3939.33</v>
-      </c>
-      <c r="O10">
-        <v>941856</v>
-      </c>
-      <c r="P10">
-        <v>931856</v>
-      </c>
-      <c r="Q10">
-        <v>4268144</v>
-      </c>
-      <c r="R10">
-        <v>3741856</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>GP01</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Meridian Growth GP III LLC</v>
-      </c>
-      <c r="C11">
-        <v>1000000</v>
-      </c>
-      <c r="D11">
-        <v>650000</v>
-      </c>
-      <c r="E11">
-        <v>350000</v>
-      </c>
-      <c r="F11">
-        <v>64583.33</v>
-      </c>
-      <c r="G11">
-        <v>35416.67</v>
-      </c>
-      <c r="H11">
-        <v>13020.83</v>
-      </c>
-      <c r="I11">
-        <v>2968.75</v>
-      </c>
-      <c r="J11">
-        <v>1250</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>117239.58</v>
-      </c>
-      <c r="P11">
-        <v>115989.58</v>
-      </c>
-      <c r="Q11">
-        <v>534010.42</v>
-      </c>
-      <c r="R11">
-        <v>467239.58</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v/>
-      </c>
-      <c r="B12" t="str">
-        <v>TOTAL</v>
-      </c>
-      <c r="C12">
-        <v>96000000</v>
-      </c>
-      <c r="D12">
-        <v>62400000</v>
-      </c>
-      <c r="E12">
-        <v>33600000</v>
-      </c>
-      <c r="F12">
-        <v>6200000</v>
-      </c>
-      <c r="G12">
-        <v>3400000</v>
-      </c>
-      <c r="H12">
-        <v>1250000</v>
-      </c>
-      <c r="I12">
-        <v>285000</v>
-      </c>
-      <c r="J12">
-        <v>120000</v>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12">
-        <v>126857.5</v>
-      </c>
-      <c r="M12">
-        <v>80500</v>
-      </c>
-      <c r="N12">
-        <v>46357.5</v>
-      </c>
-      <c r="O12">
-        <v>11301357.5</v>
-      </c>
-      <c r="P12">
-        <v>11181357.5</v>
-      </c>
-      <c r="Q12">
-        <v>51218642.5</v>
-      </c>
-      <c r="R12">
-        <v>44901357.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R12"/>
-  </ignoredErrors>
-</worksheet>
 </file>
--- a/samples/meridian-growth-partners-iii-call-4.xlsx
+++ b/samples/meridian-growth-partners-iii-call-4.xlsx
@@ -488,7 +488,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -536,128 +536,139 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Reporting_Currency</v>
+        <v>GP_Name</v>
       </c>
       <c r="B5" t="str">
-        <v>USD</v>
+        <v>Meridian Growth GP III LLC</v>
       </c>
       <c r="C5" t="str">
-        <v>ISO code.</v>
+        <v>The general partner, named in the notice letter.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Call_Number</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
+        <v>Reporting_Currency</v>
+      </c>
+      <c r="B6" t="str">
+        <v>USD</v>
       </c>
       <c r="C6" t="str">
-        <v>Integer. Increment each call.</v>
+        <v>ISO code.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Call_Date</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-11-16</v>
+        <v>Call_Number</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
       </c>
       <c r="C7" t="str">
-        <v>Effective date of the call (YYYY-MM-DD).</v>
+        <v>Integer. Increment each call.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Payment_Due_Date</v>
+        <v>Call_Date</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-11-30</v>
+        <v>2026-11-16</v>
       </c>
       <c r="C8" t="str">
-        <v>When LP wires are due.</v>
+        <v>Effective date of the call (YYYY-MM-DD).</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Default_Mgmt_Fee_Rate_Annual</v>
-      </c>
-      <c r="B9">
-        <v>0.0175</v>
+        <v>Payment_Due_Date</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-11-30</v>
       </c>
       <c r="C9" t="str">
-        <v>Fraction. 0.0175 = 1.75%.</v>
+        <v>When LP wires are due.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Default_Mgmt_Fee_Basis</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Invested_Capital</v>
+        <v>Default_Mgmt_Fee_Rate_Annual</v>
+      </c>
+      <c r="B10">
+        <v>0.0175</v>
       </c>
       <c r="C10" t="str">
-        <v>Commitment | Invested_Capital | NAV.</v>
+        <v>Fraction. 0.0175 = 1.75%.</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Mgmt_Fee_Period_Fraction</v>
-      </c>
-      <c r="B11">
-        <v>0.25</v>
+        <v>Default_Mgmt_Fee_Basis</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Invested_Capital</v>
       </c>
       <c r="C11" t="str">
-        <v>Portion of the annual fee called now. 0.25 = one quarter.</v>
+        <v>Commitment | Invested_Capital | NAV.</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Org_Expense_Cap</v>
+        <v>Mgmt_Fee_Period_Fraction</v>
       </c>
       <c r="B12">
-        <v>750000</v>
+        <v>0.25</v>
       </c>
       <c r="C12" t="str">
-        <v>Lifetime cap on organizational expenses.</v>
+        <v>Portion of the annual fee called now. 0.25 = one quarter.</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Rounding_Decimals</v>
+        <v>Org_Expense_Cap</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>750000</v>
       </c>
       <c r="C13" t="str">
-        <v>Decimal places for every allocation.</v>
+        <v>Lifetime cap on organizational expenses.</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Rounding_Plug_LP_ID</v>
-      </c>
-      <c r="B14" t="str">
-        <v>LP04</v>
+        <v>Rounding_Decimals</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
       </c>
       <c r="C14" t="str">
-        <v>Absorbs the rounding residual. Largest commitment.</v>
+        <v>Decimal places for every allocation.</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
+        <v>Rounding_Plug_LP_ID</v>
+      </c>
+      <c r="B15" t="str">
+        <v>LP04</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Absorbs the rounding residual. Largest commitment.</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
         <v>Prepared_By</v>
       </c>
-      <c r="B15" t="str">
+      <c r="B16" t="str">
         <v>Fund Administration</v>
       </c>
-      <c r="C15" t="str">
+      <c r="C16" t="str">
         <v>Traceability.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/samples/meridian-growth-partners-iii-call-4.xlsx
+++ b/samples/meridian-growth-partners-iii-call-4.xlsx
@@ -488,7 +488,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -657,18 +657,40 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
+        <v>Signatory_Name</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Priya Raghunathan</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Who signs the notice.</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Signatory_Title</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Chief Financial Officer</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Their title, under the name.</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
         <v>Prepared_By</v>
       </c>
-      <c r="B16" t="str">
+      <c r="B18" t="str">
         <v>Fund Administration</v>
       </c>
-      <c r="C16" t="str">
+      <c r="C18" t="str">
         <v>Traceability.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/samples/meridian-growth-partners-iii-call-4.xlsx
+++ b/samples/meridian-growth-partners-iii-call-4.xlsx
@@ -660,7 +660,7 @@
         <v>Signatory_Name</v>
       </c>
       <c r="B16" t="str">
-        <v>Priya Raghunathan</v>
+        <v>Baljeet Singh</v>
       </c>
       <c r="C16" t="str">
         <v>Who signs the notice.</v>
@@ -671,7 +671,7 @@
         <v>Signatory_Title</v>
       </c>
       <c r="B17" t="str">
-        <v>Chief Financial Officer</v>
+        <v>Fund Manager</v>
       </c>
       <c r="C17" t="str">
         <v>Their title, under the name.</v>
